--- a/docs/expense-sheet.xlsx
+++ b/docs/expense-sheet.xlsx
@@ -661,22 +661,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.83</v>
+        <v>7.33</v>
       </c>
       <c r="D5" t="n">
-        <v>3099</v>
+        <v>4754</v>
       </c>
       <c r="E5" t="n">
-        <v>15325343</v>
+        <v>33639287</v>
       </c>
       <c r="F5" t="n">
-        <v>2442188</v>
+        <v>4228729</v>
       </c>
       <c r="G5" t="n">
-        <v>238025088</v>
+        <v>360352896</v>
       </c>
       <c r="H5" t="n">
-        <v>255792619</v>
+        <v>398220912</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -686,12 +686,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>DeepSeek-V4.1-Flash 3099</t>
+          <t>DeepSeek-V4.1-Flash 4754</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>bash 2370 · read 944 · eval 476 · edit 367 · grep 129 · write 59</t>
+          <t>bash 3114 · read 2961 · eval 616 · edit 456 · grep 397 · write 116</t>
         </is>
       </c>
     </row>
@@ -707,22 +707,22 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>36.85</v>
+        <v>39.34</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>11043</v>
+        <v>12698</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>73354199</v>
+        <v>91668143</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>7155300</v>
+        <v>8941841</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1573100352</v>
+        <v>1695428160</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1653609851</v>
+        <v>1796038144</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>53.38</v>
@@ -1147,22 +1147,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.62</v>
+        <v>4.12</v>
       </c>
       <c r="D11" t="n">
-        <v>681</v>
+        <v>2336</v>
       </c>
       <c r="E11" t="n">
-        <v>3499969</v>
+        <v>21813913</v>
       </c>
       <c r="F11" t="n">
-        <v>840178</v>
+        <v>2626719</v>
       </c>
       <c r="G11" t="n">
-        <v>51196928</v>
+        <v>173524736</v>
       </c>
       <c r="H11" t="n">
-        <v>55537075</v>
+        <v>197965368</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1179,22 +1179,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="n">
-        <v>36.85</v>
+        <v>39.34</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>11043</v>
+        <v>12698</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>73354199</v>
+        <v>91668143</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>7155300</v>
+        <v>8941841</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1573100352</v>
+        <v>1695428160</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1653609851</v>
+        <v>1796038144</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>53.38</v>
@@ -1273,10 +1273,10 @@
         <v>128</v>
       </c>
       <c r="E2" t="n">
-        <v>2370</v>
+        <v>3114</v>
       </c>
       <c r="F2" t="n">
-        <v>5210</v>
+        <v>5954</v>
       </c>
     </row>
     <row r="3">
@@ -1295,10 +1295,10 @@
         <v>148</v>
       </c>
       <c r="E3" t="n">
-        <v>944</v>
+        <v>2961</v>
       </c>
       <c r="F3" t="n">
-        <v>3535</v>
+        <v>5552</v>
       </c>
     </row>
     <row r="4">
@@ -1317,54 +1317,54 @@
         <v>77</v>
       </c>
       <c r="E4" t="n">
-        <v>367</v>
+        <v>456</v>
       </c>
       <c r="F4" t="n">
-        <v>1432</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>eval</t>
+          <t>grep</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>160</v>
+        <v>545</v>
       </c>
       <c r="C5" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="D5" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E5" t="n">
-        <v>476</v>
+        <v>397</v>
       </c>
       <c r="F5" t="n">
-        <v>989</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>grep</t>
+          <t>eval</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>545</v>
+        <v>160</v>
       </c>
       <c r="C6" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="D6" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E6" t="n">
-        <v>129</v>
+        <v>616</v>
       </c>
       <c r="F6" t="n">
-        <v>865</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="7">
@@ -1383,10 +1383,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="F7" t="n">
-        <v>341</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8">
@@ -1405,54 +1405,54 @@
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="F8" t="n">
-        <v>240</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>advise</t>
+          <t>hub</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F9" t="n">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hub</t>
+          <t>advise</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>232</v>
       </c>
       <c r="C10" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -1471,10 +1471,10 @@
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F11" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -1493,10 +1493,10 @@
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="F12" t="n">
-        <v>122</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
@@ -1515,10 +1515,10 @@
         <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F13" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14">
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
@@ -1559,10 +1559,10 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -1581,10 +1581,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -1625,10 +1625,10 @@
         <v>498</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>4416</v>
+        <v>7864</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>13506</v>
+        <v>16954</v>
       </c>
     </row>
   </sheetData>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16 top-level sessions + 132 subagent transcripts</t>
+          <t>17 top-level sessions + 145 subagent transcripts</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-13 15:00 +08:00 (2026-09-13 07:00 UTC) — the newest activity in the corpus. The generator is deterministic w.r.t. the corpus, so re-running after new work moves the figures; both artifacts move together.</t>
+          <t>2026-09-13 23:37 +08:00 (2026-09-13 15:37 UTC) — the newest activity in the corpus. The generator is deterministic w.r.t. the corpus, so re-running after new work moves the figures; both artifacts move together.</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>36.8452 h over 22 segments</t>
+          <t>39.3399 h over 23 segments</t>
         </is>
       </c>
     </row>
